--- a/reports/pdf_rolling5_20260804.xlsx
+++ b/reports/pdf_rolling5_20260804.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,907억   ·   현금 230억(5.7%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 11종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,001억   ·   현금 232억(5.7%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>72</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3063312000</v>
+        <v>3096576000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-171</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-10999660500</v>
+        <v>-11119104000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>61</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1615886950</v>
+        <v>1633433600</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-59</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-3783251100</v>
+        <v>-3824332800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>54</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>810136620</v>
+        <v>818933760</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-27</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2882795400</v>
+        <v>-2914099200</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>414722200</v>
+        <v>419225600</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-26</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-359513700</v>
+        <v>-363417600</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2137328700</v>
+        <v>2160537600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-643052400</v>
+        <v>-650035200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2925037500</v>
+        <v>2956800000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-19</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-762181200</v>
+        <v>-770457600</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>794090700</v>
+        <v>802713600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-18</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-541549800</v>
+        <v>-547430400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>746783600</v>
+        <v>754892800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-222302850</v>
+        <v>-224716800</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>395677800</v>
+        <v>399974400</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1030828800</v>
+        <v>-1042022400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>170184000</v>
+        <v>172032000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2786763000</v>
+        <v>-2817024000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1091507500</v>
+        <v>1103360000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-3</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1130508000</v>
+        <v>-1142784000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,202억   ·   현금 26억(0.8%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,369억   ·   현금 26억(0.8%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3742490000</v>
+        <v>3728260000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>-21</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2012581200</v>
+        <v>-2004928800</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>-12</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-2004060000</v>
+        <v>-1996440000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,154억   ·   현금 92억(4.1%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 93억(4.1%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1399,7 +1399,7 @@
         <v>142</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>4085340000</v>
+        <v>4103232000</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>-41</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1363526750</v>
+        <v>-1369498400</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>50</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>2996875000</v>
+        <v>3010000000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>-17</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-4331940000</v>
+        <v>-4350912000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1560978000</v>
+        <v>1567814400</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>-13</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2827337500</v>
+        <v>-2839720000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>19</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>832960000</v>
+        <v>836608000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>-10</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-1476175000</v>
+        <v>-1482640000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>-7</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-612801000</v>
+        <v>-615484800</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,919억   ·   현금 47억(2.3%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,992억   ·   현금 47억(2.3%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1692,7 +1692,7 @@
         <v>264</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>6279240000</v>
+        <v>6297984000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>-83</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2930647000</v>
+        <v>-2939395200</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>42</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>2563554000</v>
+        <v>2571206400</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>-68</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2173212000</v>
+        <v>-2179699200</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>21</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2233612500</v>
+        <v>2240280000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>-35</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-4050987500</v>
+        <v>-4063080000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>208939500</v>
+        <v>209563200</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>-8</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-3813640000</v>
+        <v>-3825024000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억   ·   현금 14억(5.6%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 5종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억   ·   현금 14억(5.6%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 5종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -1957,11 +1957,11 @@
         <v>33</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>83853000</v>
+        <v>82046250</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>6.89%→7.41%</t>
+          <t>6.86%→7.38%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1978,11 +1978,11 @@
         <v>-152</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-636697600</v>
+        <v>-620160000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>2.59%→0.00%</t>
+          <t>2.57%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2001,11 +2001,11 @@
         <v>28</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>59505600</v>
+        <v>57225000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.40%→2.71%</t>
+          <t>2.35%→2.65%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -2022,11 +2022,11 @@
         <v>-145</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-38965850</v>
+        <v>-38171250</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.75%</t>
+          <t>2.83%→2.74%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -2045,11 +2045,11 @@
         <v>15</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>75652500</v>
+        <v>72000000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>3.45%→3.85%</t>
+          <t>3.34%→3.73%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2066,11 +2066,11 @@
         <v>-91</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-49049000</v>
+        <v>-48525750</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.84%</t>
+          <t>1.03%→0.85%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2089,11 +2089,11 @@
         <v>11</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>54292700</v>
+        <v>53542500</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>1.71%→1.97%</t>
+          <t>1.71%→1.98%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2110,11 +2110,11 @@
         <v>-6</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-117810000</v>
+        <v>-105975000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.92%→1.47%</t>
+          <t>1.75%→1.35%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2133,11 +2133,11 @@
         <v>4</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>39916800</v>
+        <v>37650000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.92%→3.16%</t>
+          <t>2.81%→3.03%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2154,11 +2154,11 @@
         <v>-3</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-71263500</v>
+        <v>-71437500</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.64%→1.39%</t>
+          <t>1.68%→1.41%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2170,7 +2170,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 446억   ·   현금 31억(6.4%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 2종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 31억(6.4%)      오늘 2026-08-04  vs  5일전 2026-07-28      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
